--- a/survey_templates/035_non_linear_equation_methods_survey--survey_templates.xlsx
+++ b/survey_templates/035_non_linear_equation_methods_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>non_linear_equation_methods_survey</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the purpose of this survey?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of the purpose of this survey.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,7 +552,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Numerical Methods Used In Signal Processing</t>
+          <t>How often do you use numerical methods in signal processing?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +565,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>numerical_methods_used_in_signal_processing</t>
+          <t>numerical_method_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>numerical-methods-used-in-signal-processing</t>
+          <t>What type of numerical method is used most often in signal processing?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +588,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>numerical_methods_used_in_signal_processing</t>
+          <t>numerical_method_selection</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>numerical-methods-used-in-signal-processing</t>
+          <t>How do you choose the type of numerical method to use in signal processing?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +616,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>numerical_methods</t>
+          <t>common_numerical_methods</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>numerical-methods</t>
+          <t>What is the most common numerical method used in signal processing?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +634,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>numerical_methods</t>
+          <t>numerical_method_validation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>numerical-methods</t>
+          <t>How do you validate the results of numerical methods in signal processing?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +657,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>numerical_methods</t>
+          <t>signal_processing_goal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>numerical-methods</t>
+          <t>What is the primary goal of using numerical methods in signal processing?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,21 +680,113 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>numerical_methods</t>
+          <t>numerical_methods_used</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>numerical-methods</t>
+          <t>What are some common numerical methods used in signal processing?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>numerical_method_selection_again</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>How do you determine the appropriate numerical method for a specific signal processing task?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>numerical_method_role</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>What is the role of numerical methods in signal processing?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>numerical_method_performance</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>How do you assess the performance of numerical methods in signal processing?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Any additional comments?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -707,12 +803,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +836,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -757,12 +853,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -774,131 +870,505 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>numerical_methods_used_in_signal_processing_choices</t>
+          <t>numerical_method_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>linear_method</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Linear method</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>numerical_methods_used_in_signal_processing_choices</t>
+          <t>numerical_method_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>non-linear_method</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Non-linear method</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>numerical_methods_used_in_signal_processing_choices</t>
+          <t>numerical_method_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>numerical_methods_choices</t>
+          <t>numerical_method_selection_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>by_experience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>By experience</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>numerical_methods_choices</t>
+          <t>numerical_method_selection_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>by_literature_review</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>By literature review</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>numerical_methods_choices</t>
+          <t>numerical_method_selection_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>by_experimentation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>By experimentation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>numerical_methods_choices</t>
+          <t>common_numerical_methods_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>least_squares_method</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Least squares method</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>common_numerical_methods_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>kalman_filter</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kalman filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>common_numerical_methods_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>wavelet_transform</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wavelet transform</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>common_numerical_methods_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>numerical_method_validation_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>by_visual_inspection</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>By visual inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>numerical_method_validation_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>by_statistical_analysis</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>By statistical analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>numerical_method_validation_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>by_experimentation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>By experimentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>signal_processing_goal_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>to_filter_out_noise</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>To filter out noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>signal_processing_goal_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>to_detect_anomalies</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>To detect anomalies</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>signal_processing_goal_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>numerical_methods_used_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>least_squares_method</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Least squares method</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>numerical_methods_used_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>kalman_filter</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Kalman filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>numerical_methods_used_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>wavelet_transform</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Wavelet transform</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>numerical_methods_used_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>numerical_method_selection_again_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>by_experience</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>By experience</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>numerical_method_selection_again_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>by_literature_review</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>By literature review</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>numerical_method_selection_again_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>by_experimentation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>By experimentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>numerical_method_role_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>to_filter_out_noise</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>To filter out noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>numerical_method_role_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>to_detect_anomalies</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>To detect anomalies</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>numerical_method_role_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>to_extract_features</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>To extract features</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>numerical_method_performance_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>by_visual_inspection</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>By visual inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>numerical_method_performance_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>by_statistical_analysis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>By statistical analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>numerical_method_performance_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
